--- a/sipii_caixa_20260721.xlsx
+++ b/sipii_caixa_20260721.xlsx
@@ -814,42 +814,42 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,29052700</t>
+          <t>2,29157700</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>6,59</t>
+          <t>6,64</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,78</t>
+          <t>12,77</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>402,686</t>
+          <t>403,112</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,56556400</t>
+          <t>5,56806700</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.667,084</t>
+          <t>6.627,413</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,81014400</t>
+          <t>2,81140700</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>824,382</t>
+          <t>817,656</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,37785000</t>
+          <t>3,37942100</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>7,20</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>14,01</t>
+          <t>14,00</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,996</t>
+          <t>11,987</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1853,42 +1853,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,03984700</t>
+          <t>3,04133700</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,61</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>14,74</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1.687,550</t>
+          <t>1.692,645</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2109,42 +2109,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>3,53521000</t>
+          <t>3,53702200</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>7,40</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>121,524</t>
+          <t>121,565</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2372,42 +2372,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,82928000</t>
+          <t>9,83379400</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>6,90</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>13,29</t>
+          <t>13,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>584,850</t>
+          <t>584,884</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2632,22 +2632,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>19,96584700</t>
+          <t>19,96081800</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>-0,400</t>
+          <t>-0,025</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -2657,17 +2657,17 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>115,421</t>
+          <t>115,405</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2896,42 +2896,42 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,40209700</t>
+          <t>3,40376400</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>7,35</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>14,16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,414</t>
+          <t>63,756</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -2959,42 +2959,178 @@
           <t>https://www.caixa.gov.br/fundos-investimento/e-fundos/renda-fixa-longo-prazo</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr"/>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr"/>
-      <c r="AD10" s="2" t="inlineStr"/>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>15.154.422/0001-99</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>RF até 49% Crédito Privado</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
       <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 90%</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AN10" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr"/>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AR10" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA E-FUNDO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS10" s="2" t="inlineStr">
+        <is>
+          <t>Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).As movimentações neste Fundo são realizadas exclusivamente pelo Internet Banking.</t>
+        </is>
+      </c>
+      <c r="AT10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AU10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AV10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AW10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AX10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AY10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AZ10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5834.pdf</t>
+        </is>
+      </c>
       <c r="BA10" s="2" t="inlineStr"/>
       <c r="BB10" s="2" t="inlineStr"/>
     </row>
@@ -3016,22 +3152,22 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1.863,07417700</t>
+          <t>1.864,09201600</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0,060</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -3041,17 +3177,17 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>97,515</t>
+          <t>97,638</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3272,42 +3408,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,58031800</t>
+          <t>13,57399300</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>-0,107</t>
+          <t>-0,046</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>5,60</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>10,67</t>
+          <t>10,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,690</t>
+          <t>27,677</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3536,22 +3672,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>46,74580900</t>
+          <t>46,76718700</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -3561,17 +3697,17 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,913</t>
+          <t>40,918</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3797,7 +3933,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,46657700</t>
+          <t>20,47607000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -3807,32 +3943,32 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>6,70</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,411</t>
+          <t>59,438</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4057,22 +4193,22 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,17137800</t>
+          <t>3,17001400</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>-0,103</t>
+          <t>-0,043</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -4082,17 +4218,17 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>77,467</t>
+          <t>77,483</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4321,22 +4457,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15,14525400</t>
+          <t>15,15222600</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>6,93</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4346,17 +4482,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,753</t>
+          <t>27,766</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4581,27 +4717,27 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,03701600</t>
+          <t>3,03835700</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>12,98</t>
+          <t>12,97</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -4611,12 +4747,12 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4837,22 +4973,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33,22076000</t>
+          <t>33,23653400</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -4862,17 +4998,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2.206,224</t>
+          <t>2.198,678</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5097,42 +5233,42 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,08314000</t>
+          <t>3,08467300</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,62</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>14,71</t>
+          <t>14,70</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.799,399</t>
+          <t>1.791,521</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5351,22 +5487,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,34907300</t>
+          <t>3,35065800</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5376,17 +5512,17 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,006</t>
+          <t>13,012</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5616,42 +5752,42 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,33530800</t>
+          <t>3,33457200</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>-0,386</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
+          <t>-0,022</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>11,59</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>130,982</t>
+          <t>130,759</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5880,42 +6016,42 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,34403100</t>
+          <t>3,34217800</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-0,263</t>
+          <t>-0,055</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,705</t>
+          <t>64,666</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6140,22 +6276,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>19,29646500</t>
+          <t>19,30625400</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -6165,17 +6301,17 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>959,523</t>
+          <t>960,526</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6400,12 +6536,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,05481800</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>0,057</t>
+          <t>1,05480300</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -6425,17 +6561,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,463</t>
+          <t>22,464</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6648,42 +6784,42 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.859,25578000</t>
+          <t>1.860,25231400</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,79</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>178,881</t>
+          <t>179,065</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6908,12 +7044,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,25926800</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>0,056</t>
+          <t>1,25925000</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -6928,22 +7064,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,57</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,952</t>
+          <t>71,866</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7160,42 +7296,42 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,12553100</t>
+          <t>1,12519450</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>-0,254</t>
+          <t>-0,029</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>4,34</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>10,20</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>201,774</t>
+          <t>201,710</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7446,12 +7582,12 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7664,22 +7800,22 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>5,01725100</t>
+          <t>5,01971700</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>7,61</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -7689,17 +7825,17 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>3.345,330</t>
+          <t>3.344,118</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7924,42 +8060,42 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10,74770400</t>
+          <t>10,75334400</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>7,52</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2.417,662</t>
+          <t>2.411,839</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8184,17 +8320,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1,18943600</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>0,055</t>
+          <t>1,18941900</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -8204,22 +8340,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>14,16</t>
+          <t>14,10</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>64,631</t>
+          <t>64,715</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8436,22 +8572,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,09329700</t>
+          <t>1,09468256</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,017</t>
+          <t>0,126</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -8461,17 +8597,17 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>311,122</t>
+          <t>311,507</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8688,22 +8824,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1,28816700</t>
+          <t>1,28881300</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>7,69</t>
+          <t>7,74</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -8713,17 +8849,17 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>437,047</t>
+          <t>436,617</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8948,42 +9084,42 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1,21608600</t>
+          <t>1,21651900</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>8,20</t>
+          <t>8,24</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>14,12</t>
+          <t>14,19</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,403</t>
+          <t>40,417</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9208,42 +9344,42 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5,59839100</t>
+          <t>5,60082100</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,80</t>
+          <t>14,79</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>558,582</t>
+          <t>560,566</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9469,42 +9605,42 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>5,21481400</t>
+          <t>5,21681300</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,60</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>14,74</t>
+          <t>14,72</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>855,883</t>
+          <t>855,727</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9729,7 +9865,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>29,62833000</t>
+          <t>29,64231100</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -9739,32 +9875,32 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>28,87</t>
+          <t>28,86</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>21,219</t>
+          <t>21,229</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9977,42 +10113,42 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1.792,75775300</t>
+          <t>1.793,42355500</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>6,47</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>13,28</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>123,535</t>
+          <t>123,239</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10233,22 +10369,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>31,04712800</t>
+          <t>31,06319100</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>7,41</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -10258,17 +10394,17 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>3.128,657</t>
+          <t>3.127,401</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10489,7 +10625,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3,26903900</t>
+          <t>3,27075100</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -10499,12 +10635,12 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,63</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -10514,17 +10650,17 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>642,959</t>
+          <t>645,912</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10749,22 +10885,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>6,27522500</t>
+          <t>6,27841700</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -10774,17 +10910,17 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>122,245</t>
+          <t>121,949</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -11010,22 +11146,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,62117400</t>
+          <t>3,62298200</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -11035,17 +11171,17 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16.104,795</t>
+          <t>16.105,679</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11274,42 +11410,42 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,38222800</t>
+          <t>5,38443600</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,70</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>7,73</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>15,11</t>
+          <t>15,10</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.487,307</t>
+          <t>1.487,240</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11535,7 +11671,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,72372100</t>
+          <t>30,73804700</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -11545,32 +11681,32 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>13,13</t>
+          <t>13,12</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>166,121</t>
+          <t>166,106</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11829,12 +11965,12 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -12051,22 +12187,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3,65616600</t>
+          <t>3,65784400</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -12076,17 +12212,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2.248,830</t>
+          <t>2.249,494</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12315,7 +12451,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2,84461900</t>
+          <t>2,84593500</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -12325,32 +12461,32 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>12,95</t>
+          <t>12,94</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>6.023,708</t>
+          <t>6.006,121</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12575,7 +12711,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,30922500</t>
+          <t>1,30990500</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -12585,32 +12721,32 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>70,953</t>
+          <t>70,777</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12835,42 +12971,42 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>3,23381300</t>
+          <t>3,23536700</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>14,88</t>
+          <t>14,87</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>14.222,772</t>
+          <t>14.057,093</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -13095,42 +13231,42 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>9,82357000</t>
+          <t>9,82811500</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,44</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>828,005</t>
+          <t>827,496</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13360,7 +13496,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,52014100</t>
+          <t>4,52245900</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -13370,32 +13506,32 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,45</t>
+          <t>14,44</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>16.665,521</t>
+          <t>16.613,050</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13620,22 +13756,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,17667000</t>
+          <t>5,17916000</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -13645,17 +13781,17 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>22.055,983</t>
+          <t>22.045,844</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13880,42 +14016,42 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4,84428100</t>
+          <t>4,84658100</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,62</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,71</t>
+          <t>14,70</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>9.653,957</t>
+          <t>9.635,886</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -14144,7 +14280,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.754,14668500</t>
+          <t>1.755,03051100</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -14154,12 +14290,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,31</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -14169,17 +14305,17 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>272,228</t>
+          <t>273,543</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14207,42 +14343,182 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="inlineStr"/>
-      <c r="X54" s="2" t="inlineStr"/>
-      <c r="Y54" s="2" t="inlineStr"/>
-      <c r="Z54" s="2" t="inlineStr"/>
-      <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
-      <c r="AC54" s="2" t="inlineStr"/>
-      <c r="AD54" s="2" t="inlineStr"/>
-      <c r="AE54" s="2" t="inlineStr"/>
-      <c r="AF54" s="2" t="inlineStr"/>
-      <c r="AG54" s="2" t="inlineStr"/>
-      <c r="AH54" s="2" t="inlineStr"/>
-      <c r="AI54" s="2" t="inlineStr"/>
-      <c r="AJ54" s="2" t="inlineStr"/>
-      <c r="AK54" s="2" t="inlineStr"/>
-      <c r="AL54" s="2" t="inlineStr"/>
-      <c r="AM54" s="2" t="inlineStr"/>
-      <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>RF 100% TPF - Curto Prazo</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
+          <t>CURTO PRAZO</t>
+        </is>
+      </c>
+      <c r="AF54" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AG54" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AH54" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AI54" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AJ54" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AL54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AM54" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AN54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AP54" s="2" t="inlineStr"/>
-      <c r="AQ54" s="2" t="inlineStr"/>
-      <c r="AR54" s="2" t="inlineStr"/>
-      <c r="AS54" s="2" t="inlineStr"/>
-      <c r="AT54" s="2" t="inlineStr"/>
-      <c r="AU54" s="2" t="inlineStr"/>
-      <c r="AV54" s="2" t="inlineStr"/>
-      <c r="AW54" s="2" t="inlineStr"/>
-      <c r="AX54" s="2" t="inlineStr"/>
-      <c r="AY54" s="2" t="inlineStr"/>
-      <c r="AZ54" s="2" t="inlineStr"/>
+      <c r="AQ54" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AR54" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CURTO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS54" s="2" t="inlineStr">
+        <is>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
+      <c r="AT54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AU54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AV54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AW54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AX54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AY54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AZ54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6520.pdf</t>
+        </is>
+      </c>
       <c r="BA54" s="2" t="inlineStr"/>
       <c r="BB54" s="2" t="inlineStr"/>
     </row>
@@ -14264,17 +14540,17 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,43839800</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>0,040</t>
+          <t>1,43839600</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -14284,22 +14560,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>14,42</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>64,904</t>
+          <t>64,791</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14516,27 +14792,27 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>12,71733100</t>
+          <t>12,71030300</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>-0,125</t>
+          <t>-0,055</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>17,52</t>
+          <t>17,94</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -14546,12 +14822,12 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14780,12 +15056,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.650,88372300</t>
+          <t>1.650,78158200</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>-0,185</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -14800,22 +15076,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>12,07</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>113,745</t>
+          <t>113,723</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15036,42 +15312,42 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2.455,05181100</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-0,090</t>
+          <t>2.466,70284900</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>0,474</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>19,52</t>
+          <t>20,09</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>32,66</t>
+          <t>34,28</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>12,990</t>
+          <t>13,093</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15322,12 +15598,12 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15544,42 +15820,42 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1,26441800</t>
+          <t>1,26397200</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>-0,022</t>
+          <t>-0,035</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,62</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>5,751</t>
+          <t>5,749</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15800,42 +16076,42 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,11654300</t>
+          <t>1,10737800</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>-0,743</t>
+          <t>-0,820</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>-0,70</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-3,70</t>
+          <t>-4,49</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>14,16</t>
+          <t>15,83</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>3,472</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16086,12 +16362,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16308,12 +16584,12 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,38979000</t>
+          <t>1,38971900</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>-0,649</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -16323,27 +16599,27 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,80</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>14,73</t>
+          <t>15,65</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>11,596</t>
+          <t>11,599</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16594,12 +16870,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16816,42 +17092,42 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,10611400</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>0,153</t>
+          <t>1,10019300</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>-0,535</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-8,25</t>
+          <t>-8,75</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>-7,39</t>
+          <t>-8,93</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>3,747</t>
+          <t>3,727</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -17072,22 +17348,22 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>5,39653900</t>
+          <t>5,39634433</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>-0,131</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -17097,17 +17373,17 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>32,637</t>
+          <t>32,629</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17332,17 +17608,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1.222,36694100</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>0,143</t>
+          <t>1.222,32881300</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -17350,24 +17626,24 @@
           <t>-2,58</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>0,55</t>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>37,156</t>
+          <t>37,161</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17602,42 +17878,42 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,24672600</t>
+          <t>4,24935300</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>0,663</t>
+          <t>0,061</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>-4,36</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>26,80</t>
+          <t>26,33</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>506,678</t>
+          <t>505,626</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17862,42 +18138,42 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,85371400</t>
+          <t>2,85356400</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>-0,483</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,80</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>9,32</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>71,657</t>
+          <t>71,653</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18118,42 +18394,42 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.711,04977400</t>
+          <t>1.714,56994400</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>0,329</t>
+          <t>0,205</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>8,60</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>14,08</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>30,445</t>
+          <t>30,504</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18378,42 +18654,42 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,80743700</t>
+          <t>3,80064900</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>-0,956</t>
+          <t>-0,178</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>13,18</t>
+          <t>12,98</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>29,04</t>
+          <t>28,86</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.373,002</t>
+          <t>2.368,561</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18638,42 +18914,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,92921500</t>
+          <t>1,92990700</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,032</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>12,59</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,634</t>
+          <t>21,619</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18898,12 +19174,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.674,14129000</t>
+          <t>1.674,09006300</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>-0,180</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -18918,22 +19194,22 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>13,03</t>
+          <t>13,04</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,209</t>
+          <t>14,133</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19154,42 +19430,42 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>5,68728100</t>
+          <t>5,68683200</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>-0,144</t>
+          <t>-0,007</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>13,95</t>
+          <t>13,92</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>896,268</t>
+          <t>896,182</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19414,17 +19690,17 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0,46702100</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>0,041</t>
+          <t>0,46699485</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
@@ -19444,12 +19720,12 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19681,22 +19957,22 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3,69858100</t>
+          <t>3,69996500</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>0,033</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -19706,17 +19982,17 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>719,063</t>
+          <t>718,090</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19937,12 +20213,12 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,38959100</t>
+          <t>1,38953700</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>-0,133</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -19957,22 +20233,22 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>8,64</t>
+          <t>8,72</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>71,209</t>
+          <t>71,206</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20205,12 +20481,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,50106200</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>0,048</t>
+          <t>1,50100600</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -20225,22 +20501,22 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>12,42</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>194,628</t>
+          <t>194,621</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20473,12 +20749,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>3,35940200</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>0,220</t>
+          <t>3,35920700</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -20493,22 +20769,22 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>160,003</t>
+          <t>159,994</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20739,12 +21015,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,55918100</t>
+          <t>1,55910900</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>-0,262</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -20754,12 +21030,12 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>21,98</t>
+          <t>23,23</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -20769,12 +21045,12 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -21005,42 +21281,42 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>6,86545000</t>
+          <t>6,86516400</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>-0,008</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>15,97</t>
+          <t>16,08</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>128,001</t>
+          <t>128,055</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21261,17 +21537,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,80353100</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>0,038</t>
+          <t>1,80349400</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -21281,22 +21557,22 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>10,74</t>
+          <t>10,63</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>173,553</t>
+          <t>173,559</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21517,7 +21793,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,44124200</t>
+          <t>1,44144600</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -21527,32 +21803,32 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>14,65</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>285,453</t>
+          <t>285,488</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21778,17 +22054,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,34930100</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>0,330</t>
+          <t>1,34927300</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -21798,22 +22074,22 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>12,511</t>
+          <t>12,185</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22038,42 +22314,42 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,82885000</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>0,188</t>
+          <t>3,81460100</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>-0,372</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-5,10</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>-3,71</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,245</t>
+          <t>95,871</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22298,42 +22574,42 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,83317300</t>
+          <t>6,82018700</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>-0,242</t>
+          <t>-0,190</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>7,73</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>24,84</t>
+          <t>26,11</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>332,484</t>
+          <t>331,865</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22558,42 +22834,42 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,58318400</t>
+          <t>2,57812000</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>-0,066</t>
+          <t>-0,196</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>7,36</t>
+          <t>7,15</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>27,00</t>
+          <t>28,79</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,232</t>
+          <t>13,208</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22818,42 +23094,42 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.854,44268000</t>
+          <t>1.837,49855400</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>-0,794</t>
+          <t>-0,913</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-6,58</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>11,57</t>
+          <t>12,84</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>9,262</t>
+          <t>9,177</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -23067,42 +23343,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,01044600</t>
+          <t>9,96576700</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>-0,940</t>
+          <t>-0,446</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>12,91</t>
+          <t>11,62</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>272,625</t>
+          <t>271,270</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -23327,42 +23603,42 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,41617300</t>
+          <t>1,40319000</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>-1,063</t>
+          <t>-0,916</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-3,03</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-7,10</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>-0,59</t>
+          <t>-7,95</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>0,80</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>424,919</t>
+          <t>421,015</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23587,42 +23863,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,06434100</t>
+          <t>1,05597800</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>-0,698</t>
+          <t>-0,785</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-3,61</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-8,55</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>-1,21</t>
+          <t>-9,27</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>54,437</t>
+          <t>53,993</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23847,42 +24123,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,72314900</t>
+          <t>1,71337800</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>-0,472</t>
+          <t>-0,567</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>13,20</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,121</t>
+          <t>2,109</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -24107,42 +24383,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,48418000</t>
+          <t>4,51374300</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>2,569</t>
+          <t>0,659</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>42,39</t>
+          <t>43,33</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>41,58</t>
+          <t>44,63</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>74,558</t>
+          <t>75,014</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24367,42 +24643,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,64333700</t>
+          <t>8,62603400</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>-0,070</t>
+          <t>-0,200</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>25,65</t>
+          <t>27,43</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>85,842</t>
+          <t>85,647</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24627,42 +24903,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,26136400</t>
+          <t>1,26098400</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,578</t>
+          <t>-0,030</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>11,92</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>284,378</t>
+          <t>284,293</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24887,42 +25163,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,75059800</t>
+          <t>1,72802800</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>-1,575</t>
+          <t>-1,289</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>-8,66</t>
+          <t>-9,83</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-7,93</t>
+          <t>-9,11</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>10,34</t>
+          <t>11,45</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>106,040</t>
+          <t>104,590</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -25147,42 +25423,42 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,86895400</t>
+          <t>2,85884600</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>-0,180</t>
+          <t>-0,352</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>19,06</t>
+          <t>20,48</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>124,256</t>
+          <t>123,816</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25407,42 +25683,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,79977800</t>
+          <t>1,78328200</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>-0,797</t>
+          <t>-0,916</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-7,11</t>
+          <t>-7,96</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>11,59</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>47,252</t>
+          <t>46,824</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25671,42 +25947,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,35867200</t>
+          <t>6,39659900</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>2,475</t>
+          <t>0,596</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>35,57</t>
+          <t>36,37</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>39,43</t>
+          <t>42,37</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>113,607</t>
+          <t>114,263</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25931,42 +26207,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.291,86528400</t>
+          <t>1.271,67669400</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>-1,302</t>
+          <t>-1,562</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-5,49</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>-0,27</t>
+          <t>-6,97</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>0,49</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>42,125</t>
+          <t>41,493</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26191,42 +26467,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>34,45212900</t>
+          <t>33,97479100</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>-0,062</t>
+          <t>-1,385</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>-6,40</t>
+          <t>-7,70</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>42,07</t>
+          <t>39,45</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>580,733</t>
+          <t>573,555</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26451,42 +26727,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>3,34029000</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>-1,071</t>
+          <t>3,37343400</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>0,992</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>11,86</t>
+          <t>12,97</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>37,89</t>
+          <t>39,26</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>70,00</t>
+          <t>72,67</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>545,119</t>
+          <t>550,203</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26711,42 +26987,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,70199700</t>
+          <t>4,68855900</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>-0,244</t>
+          <t>-0,285</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-1,96</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>24,80</t>
+          <t>26,40</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>22,925</t>
+          <t>22,859</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26971,42 +27247,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.556,61586200</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>-0,936</t>
+          <t>1.557,99936900</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>0,088</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>23,05</t>
+          <t>26,61</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>31,131</t>
+          <t>31,172</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27231,42 +27507,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,92732100</t>
+          <t>1,91397300</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>-0,420</t>
+          <t>-0,692</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>-5,92</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>10,73</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,728</t>
+          <t>1,718</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27483,42 +27759,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,82335700</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>0,087</t>
+          <t>5,80834500</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>-0,257</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>8,25</t>
+          <t>7,97</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>28,11</t>
+          <t>29,94</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>42,600</t>
+          <t>42,469</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27735,42 +28011,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,20695100</t>
+          <t>2,20075900</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>-0,429</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>0,18</t>
+          <t>-0,280</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>-0,10</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>24,16</t>
+          <t>25,76</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,300</t>
+          <t>35,222</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -27995,42 +28271,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>41,59446300</t>
+          <t>41,86801800</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2,562</t>
+          <t>0,657</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>42,47</t>
+          <t>43,40</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>41,71</t>
+          <t>44,75</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>811,830</t>
+          <t>817,192</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28255,42 +28531,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,83892800</t>
+          <t>0,83165600</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>-0,332</t>
+          <t>-0,866</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,90</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-12,84</t>
+          <t>-13,60</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-15,87</t>
+          <t>-15,08</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,877</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28511,42 +28787,42 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,23370200</t>
+          <t>1,22762800</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>-0,302</t>
+          <t>-0,492</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>18,34</t>
+          <t>18,81</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,808</t>
+          <t>3,784</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28767,42 +29043,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,64986700</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>-1,072</t>
+          <t>1,66623400</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>0,992</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>11,86</t>
+          <t>12,97</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>37,78</t>
+          <t>39,15</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>69,76</t>
+          <t>72,43</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>24,028</t>
+          <t>24,266</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -29027,42 +29303,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,70060100</t>
+          <t>1,70594500</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>0,935</t>
+          <t>0,314</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>-7,67</t>
+          <t>-7,38</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>71,50</t>
+          <t>72,83</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>260,433</t>
+          <t>261,137</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -29291,12 +29567,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1.003,86900300</t>
+          <t>1.003,83563900</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>-0,304</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -29311,22 +29587,22 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>19,97</t>
+          <t>21,60</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>8,113</t>
+          <t>8,112</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29551,42 +29827,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.490,28163000</t>
+          <t>1.490,24143200</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>-0,311</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>14,89</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>21,452</t>
+          <t>21,451</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29807,42 +30083,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>169,65388401</t>
+          <t>169,32938296</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>-0,053</t>
+          <t>-0,191</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>27,65</t>
+          <t>29,45</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>16,967</t>
+          <t>16,934</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -30067,42 +30343,42 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,73768400</t>
+          <t>1,74315200</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>0,932</t>
+          <t>0,314</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>-7,33</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>71,81</t>
+          <t>73,15</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>4,857</t>
+          <t>4,872</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30324,42 +30600,42 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,69468400</t>
+          <t>1,70005900</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>0,941</t>
+          <t>0,317</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>-7,67</t>
+          <t>-7,37</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>-1,00</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>71,84</t>
+          <t>73,18</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.532,646</t>
+          <t>1.537,390</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30577,42 +30853,42 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>46,29521800</t>
+          <t>46,60096300</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2,567</t>
+          <t>0,660</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>42,94</t>
+          <t>43,88</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>42,50</t>
+          <t>45,56</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>663,465</t>
+          <t>667,300</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30821,42 +31097,42 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>38,18526600</t>
+          <t>37,65563100</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>-0,060</t>
+          <t>-1,387</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>-6,40</t>
+          <t>-7,70</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>42,81</t>
+          <t>40,17</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>680,606</t>
+          <t>670,670</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -31065,42 +31341,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>15,95835700</t>
+          <t>15,79614900</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>-0,881</t>
+          <t>-1,016</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-5,38</t>
+          <t>-6,34</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>13,47</t>
+          <t>14,90</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>108,561</t>
+          <t>107,458</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31318,42 +31594,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>32,00338400</t>
+          <t>31,56158700</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>-0,062</t>
+          <t>-1,380</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>-7,68</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>41,89</t>
+          <t>39,28</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>11,057</t>
+          <t>10,904</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31567,42 +31843,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>40,89050700</t>
+          <t>41,16028400</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2,568</t>
+          <t>0,659</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>42,62</t>
+          <t>43,56</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>41,88</t>
+          <t>44,93</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>571,022</t>
+          <t>574,453</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31627,17 +31903,17 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-4</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-2</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>03.555.959/0001-81</t>
+          <t>03.915.910/0001-92</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
@@ -31647,12 +31923,12 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="U122" s="2" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="V122" s="2" t="inlineStr">
@@ -31697,7 +31973,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>Fechado para captação</t>
+          <t>Aberto para captação</t>
         </is>
       </c>
       <c r="AE122" s="2" t="inlineStr">
@@ -31710,7 +31986,11 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AH122" s="2" t="inlineStr">
         <is>
           <t>17h00</t>
@@ -31747,47 +32027,48 @@
       </c>
       <c r="AR122" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - PETROBRAS IV - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - PETROBRAS II - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS122" s="2" t="inlineStr">
         <is>
-          <t>FUNDO FECHADO.</t>
+          <t>O fundo encontra-se aberto para receber recursos provenientes de outros Fundos FMP-FGTS.
+Prazo de carência: 6 meses para transferência total ou parcial do investimento no FUNDO para outro FMP- FGTS ou para um Clube de Investimento – FGTS, ou 12 meses para retorno à(s) conta(s) vinculada(s) do investidor junto ao FGTS.</t>
         </is>
       </c>
       <c r="AT122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5204.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5202.pdf</t>
         </is>
       </c>
       <c r="AU122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5204.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5202.pdf</t>
         </is>
       </c>
       <c r="AV122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5202.pdf</t>
         </is>
       </c>
       <c r="AW122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5202.pdf</t>
         </is>
       </c>
       <c r="AX122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5202.pdf</t>
         </is>
       </c>
       <c r="AY122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5202.pdf</t>
         </is>
       </c>
       <c r="AZ122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5202.pdf</t>
         </is>
       </c>
       <c r="BA122" s="2" t="inlineStr"/>
@@ -31811,42 +32092,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>32,85771100</t>
+          <t>32,40029500</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>-0,062</t>
+          <t>-1,392</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-7,73</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-1,67</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>42,07</t>
+          <t>39,44</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>409,533</t>
+          <t>403,819</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -32055,42 +32336,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>43,48494000</t>
+          <t>43,77221900</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>2,571</t>
+          <t>0,660</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>42,79</t>
+          <t>43,74</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>42,18</t>
+          <t>45,23</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>656,667</t>
+          <t>660,780</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32303,7 +32584,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,14075600</t>
+          <t>1,14128400</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -32313,12 +32594,12 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -32328,17 +32609,17 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>61,500</t>
+          <t>63,248</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32564,7 +32845,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,37678300</t>
+          <t>1,37742400</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -32574,12 +32855,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -32589,17 +32870,17 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>199,268</t>
+          <t>168,202</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32829,42 +33110,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,97746700</t>
+          <t>5,98045000</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>13,89</t>
+          <t>13,88</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,475</t>
+          <t>41,444</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -33090,7 +33371,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,20482500</t>
+          <t>5,20750500</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -33100,12 +33381,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>7,50</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -33115,17 +33396,17 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>803,803</t>
+          <t>804,216</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -33155,12 +33436,12 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>09.548.725/0001-93</t>
+          <t>09.181.268/0001-41</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="S128" s="2" t="inlineStr">
@@ -33170,12 +33451,12 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
         <is>
-          <t>10000000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="V128" s="2" t="inlineStr">
@@ -33190,7 +33471,7 @@
       </c>
       <c r="X128" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Y128" s="2" t="inlineStr">
@@ -33230,7 +33511,7 @@
       </c>
       <c r="AF128" s="2" t="inlineStr">
         <is>
-          <t>QUALIFICADO</t>
+          <t>GERAL</t>
         </is>
       </c>
       <c r="AG128" s="2" t="inlineStr">
@@ -33278,7 +33559,7 @@
       </c>
       <c r="AR128" s="2" t="inlineStr">
         <is>
-          <t>CAIXA SAUDE SUPLEMENTAR - ANS II FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA SAÚDE SUPLEMENTAR - ANS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS128" s="2" t="inlineStr">
@@ -33293,37 +33574,37 @@
       </c>
       <c r="AT128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5132.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5080.pdf</t>
         </is>
       </c>
       <c r="AU128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5132.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5080.pdf</t>
         </is>
       </c>
       <c r="AV128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5080.pdf</t>
         </is>
       </c>
       <c r="AW128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5080.pdf</t>
         </is>
       </c>
       <c r="AX128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5080.pdf</t>
         </is>
       </c>
       <c r="AY128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5080.pdf</t>
         </is>
       </c>
       <c r="AZ128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5080.pdf</t>
         </is>
       </c>
       <c r="BA128" s="2" t="inlineStr"/>
@@ -33347,7 +33628,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,26855300</t>
+          <t>3,27019300</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -33357,32 +33638,32 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,30</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>25,612</t>
+          <t>25,295</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33609,22 +33890,22 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,99480200</t>
+          <t>23,98514200</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>-0,100</t>
+          <t>-0,040</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
@@ -33634,17 +33915,17 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,835</t>
+          <t>94,797</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33873,7 +34154,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,32439900</t>
+          <t>3,32608100</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -33883,32 +34164,32 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>7,30</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>14,18</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>8.039,618</t>
+          <t>7.857,337</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -34134,22 +34415,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>4,95704300</t>
+          <t>4,95958000</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -34159,17 +34440,17 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>3.051,322</t>
+          <t>3.043,804</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -34394,42 +34675,42 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>1.918,08529800</t>
+          <t>1.919,05038100</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,70</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>7,80</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>15,08</t>
+          <t>15,07</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>16.910,270</t>
+          <t>16.822,395</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34654,7 +34935,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,57429923</t>
+          <t>1,57512070</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -34664,12 +34945,12 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -34679,17 +34960,17 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>360,266</t>
+          <t>357,694</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34898,7 +35179,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,20822800</t>
+          <t>5,21096200</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -34908,32 +35189,32 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>14,72</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>310,014</t>
+          <t>310,176</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -35155,22 +35436,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>18,20429700</t>
+          <t>18,21373100</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>7,52</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -35180,17 +35461,17 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.804,012</t>
+          <t>4.806,501</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35399,22 +35680,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>8,84972500</t>
+          <t>8,85429700</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -35424,17 +35705,17 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>3.954,451</t>
+          <t>3.929,995</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35647,22 +35928,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,86646700</t>
+          <t>2,86781600</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>6,84</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -35672,17 +35953,17 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>14.012,145</t>
+          <t>13.732,680</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35908,42 +36189,42 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1,39699600</t>
+          <t>1,39773300</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>7,69</t>
+          <t>7,74</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>14,98</t>
+          <t>14,97</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>3.619,932</t>
+          <t>3.605,755</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36164,7 +36445,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>4,50114100</t>
+          <t>4,50349800</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -36174,32 +36455,32 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>14.285,555</t>
+          <t>14.261,938</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36434,7 +36715,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.801,29172700</t>
+          <t>1.802,22758300</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -36444,12 +36725,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>7,49</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -36459,17 +36740,17 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.669,723</t>
+          <t>1.672,295</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36694,7 +36975,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,32533900</t>
+          <t>1,32590500</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -36704,12 +36985,12 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -36719,17 +37000,17 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>35.073,508</t>
+          <t>34.957,301</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36953,7 +37234,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,53759800</t>
+          <t>9,54197700</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -36963,12 +37244,12 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>6,60</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -36978,17 +37259,17 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.929,250</t>
+          <t>3.022,776</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -37212,7 +37493,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,51169000</t>
+          <t>2,51284300</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -37222,32 +37503,32 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>6,54</t>
+          <t>6,59</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>12,53</t>
+          <t>12,54</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>18.735,160</t>
+          <t>18.690,567</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37473,22 +37754,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,64947200</t>
+          <t>2,65080900</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>7,63</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -37498,17 +37779,17 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.029,943</t>
+          <t>9.005,300</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37737,12 +38018,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,42679000</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>-0,102</t>
+          <t>2,42680000</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -37762,17 +38043,17 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.411,671</t>
+          <t>3.411,838</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -38002,42 +38283,42 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>3,01106300</t>
+          <t>3,00984500</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>-0,100</t>
+          <t>-0,040</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>36,520</t>
+          <t>36,505</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38258,42 +38539,42 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.663,28039400</t>
+          <t>1.664,07075300</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>0,025</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>12,60</t>
+          <t>12,70</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>463,545</t>
+          <t>463,765</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38518,42 +38799,42 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,55111800</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>-0,014</t>
+          <t>4,55402100</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>0,063</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,31</t>
+          <t>14,34</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.234,946</t>
+          <t>11.247,798</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38785,42 +39066,42 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,85119700</t>
+          <t>3,84805800</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>-0,133</t>
+          <t>-0,081</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,80</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>3.036,161</t>
+          <t>3.030,789</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -39048,42 +39329,42 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,66213400</t>
+          <t>3,66140200</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>-0,384</t>
-        </is>
-      </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>0,02</t>
+          <t>-0,019</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>0,00</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>4,90</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>12,12</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.664,582</t>
+          <t>1.664,711</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39315,42 +39596,42 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,16362600</t>
+          <t>5,16100700</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>-0,255</t>
+          <t>-0,050</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>10,39</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.323,867</t>
+          <t>2.319,689</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39571,22 +39852,22 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,23495700</t>
+          <t>5,23284300</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>-0,104</t>
+          <t>-0,040</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -39596,17 +39877,17 @@
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.591,684</t>
+          <t>5.600,830</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39827,42 +40108,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,80027400</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>-0,107</t>
+          <t>4,80089300</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>0,012</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,03</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>478,382</t>
+          <t>478,444</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -40089,22 +40370,22 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>8,07266700</t>
+          <t>8,07673200</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -40114,17 +40395,17 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>181,323</t>
+          <t>181,620</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40209,42 +40490,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,44552100</t>
+          <t>3,44326300</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>-0,373</t>
+          <t>-0,065</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>3,20</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>754,268</t>
+          <t>753,774</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40465,42 +40746,42 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,78474300</t>
+          <t>3,78291100</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>-0,509</t>
+          <t>-0,048</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-0,20</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>11,46</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>662,313</t>
+          <t>661,993</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40732,22 +41013,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,28719300</t>
+          <t>7,29090600</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -40757,17 +41038,17 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.794,345</t>
+          <t>12.705,391</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40997,7 +41278,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,61210300</t>
+          <t>7,61602800</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -41007,32 +41288,32 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>7,50</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>14,48</t>
+          <t>14,47</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>3.791,824</t>
+          <t>3.790,116</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41257,22 +41538,22 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,46300700</t>
+          <t>1,46271600</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>-0,330</t>
+          <t>-0,019</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>4,90</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
@@ -41282,17 +41563,17 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>156,774</t>
+          <t>156,743</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41513,7 +41794,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,18694100</t>
+          <t>3,18851600</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -41523,12 +41804,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>7,10</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -41538,17 +41819,17 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.716,570</t>
+          <t>1.829,417</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41771,42 +42052,42 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,83050800</t>
+          <t>6,83377800</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>23.292,617</t>
+          <t>23.224,903</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41891,42 +42172,42 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,53374700</t>
+          <t>5,53081900</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>-0,261</t>
+          <t>-0,052</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>10,27</t>
+          <t>10,34</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>584,706</t>
+          <t>584,397</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42152,42 +42433,42 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1.564,27146300</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="inlineStr">
-        <is>
-          <t>-0,184</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>5,38</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>12,09</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>130,347</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42404,42 +42685,42 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,89672700</t>
+          <t>3,88913100</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>-0,064</t>
+          <t>-0,194</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,41</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>27,63</t>
+          <t>29,43</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>286,123</t>
+          <t>285,378</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42660,42 +42941,42 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,58245900</t>
+          <t>3,57532300</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>-0,059</t>
+          <t>-0,199</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>7,23</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>27,14</t>
+          <t>28,94</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>7,467</t>
+          <t>7,452</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42920,42 +43201,42 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,23160418</t>
+          <t>11,18162916</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>-0,941</t>
+          <t>-0,444</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>12,51</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.277,403</t>
+          <t>2.264,246</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43180,42 +43461,42 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>1,99895800</t>
+          <t>1,99427700</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>-0,328</t>
+          <t>-0,234</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>-0,20</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>23,36</t>
+          <t>25,13</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>195,330</t>
+          <t>194,873</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43436,42 +43717,42 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>1,92595500</t>
+          <t>1,90825100</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>-0,799</t>
+          <t>-0,919</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>-7,10</t>
+          <t>-7,95</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>11,62</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>721,146</t>
+          <t>714,517</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43696,42 +43977,42 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,48260324</t>
+          <t>3,47588667</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>-0,284</t>
+          <t>-0,192</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>6,84</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>23,06</t>
+          <t>24,68</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.335,498</t>
+          <t>1.332,923</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43948,7 +44229,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,49212902</t>
+          <t>2,48581813</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -43958,32 +44239,32 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,32</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>22,90</t>
+          <t>24,96</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>762,837</t>
+          <t>760,905</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44200,42 +44481,42 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,80712600</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>-0,010</t>
+          <t>3,80945800</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>0,061</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,28</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>5.158,179</t>
+          <t>4.671,550</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
